--- a/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/site_eval_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3.2004</v>
@@ -538,19 +538,19 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>3.3528</v>
@@ -591,19 +591,19 @@
         <v>1.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -618,15 +618,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>6.2484</v>
@@ -644,19 +644,19 @@
         <v>1.57</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         <v>0.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -750,19 +750,19 @@
         <v>1.795</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>1.81</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>9.144</v>
@@ -856,19 +856,19 @@
         <v>1.45</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K8" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.8333333333333334</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         <v>3.99</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>10.668</v>
@@ -962,19 +962,19 @@
         <v>2.18</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K10" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.8333333333333334</v>
-      </c>
       <c r="M10" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1015,19 +1015,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="J11" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2</v>
-      </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1068,19 +1068,19 @@
         <v>0.88</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1095,15 +1095,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1.524</v>
@@ -1121,19 +1121,19 @@
         <v>7.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1148,15 +1148,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1.3716</v>
@@ -1174,19 +1174,19 @@
         <v>3.61</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>6.7056</v>
@@ -1227,19 +1227,19 @@
         <v>2.13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1280,19 +1280,19 @@
         <v>1.25</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1311,11 +1311,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>7.62</v>
@@ -1333,19 +1333,19 @@
         <v>1.12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>5.486400000000001</v>
@@ -1386,19 +1386,19 @@
         <v>1.53</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1439,19 +1439,19 @@
         <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1477,34 +1477,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.43256</v>
+        <v>3.9624</v>
       </c>
       <c r="F20" t="n">
-        <v>9.52</v>
+        <v>5.75</v>
       </c>
       <c r="G20" t="n">
-        <v>17.02</v>
+        <v>17.11</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1515,49 +1515,49 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>7.9248</v>
+        <v>1.43256</v>
       </c>
       <c r="F21" t="n">
-        <v>9.77</v>
+        <v>9.52</v>
       </c>
       <c r="G21" t="n">
-        <v>16.43</v>
+        <v>17.02</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="I21" t="n">
-        <v>1.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1580,37 +1580,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3716</v>
+        <v>7.9248</v>
       </c>
       <c r="F22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="G22" t="n">
-        <v>20.5</v>
+        <v>16.43</v>
       </c>
       <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>1.16</v>
       </c>
-      <c r="I22" t="n">
-        <v>1.82</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1629,41 +1629,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>1.8288</v>
       </c>
       <c r="F23" t="n">
-        <v>8.039999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="G23" t="n">
-        <v>26.89</v>
+        <v>20.62</v>
       </c>
       <c r="H23" t="n">
-        <v>1.611842946668372</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="I23" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M23" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N23" t="n">
-        <v>0.625</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1689,34 +1689,34 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>1.3716</v>
       </c>
       <c r="F24" t="n">
-        <v>10.12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>19.12</v>
+        <v>20.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1.541641360461585</v>
+        <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>1.08693561108866</v>
+        <v>1.82</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1739,37 +1739,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="G25" t="n">
-        <v>18.02</v>
+        <v>20.77</v>
       </c>
       <c r="H25" t="n">
-        <v>1.162022194821208</v>
+        <v>1.433404487688642</v>
       </c>
       <c r="I25" t="n">
-        <v>1.71138107667851</v>
+        <v>0.41342143147169</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1780,11 +1780,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1792,37 +1792,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F26" t="n">
-        <v>10.2</v>
+        <v>10.12</v>
       </c>
       <c r="G26" t="n">
-        <v>19.35</v>
+        <v>19.12</v>
       </c>
       <c r="H26" t="n">
-        <v>1.086738836265223</v>
+        <v>1.541641360461585</v>
       </c>
       <c r="I26" t="n">
-        <v>0.806961722029484</v>
+        <v>1.08693561108866</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1848,34 +1848,34 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>9.789999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="G27" t="n">
-        <v>19.2</v>
+        <v>19.57</v>
       </c>
       <c r="H27" t="n">
-        <v>1.698140741541455</v>
+        <v>1.62995516333357</v>
       </c>
       <c r="I27" t="n">
-        <v>2.16766115621638</v>
+        <v>1.50490599353894</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1901,34 +1901,34 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>17.91</v>
+        <v>18.02</v>
       </c>
       <c r="H28" t="n">
-        <v>1.699273096764108</v>
+        <v>1.162022194821208</v>
       </c>
       <c r="I28" t="n">
-        <v>1.05926908510679</v>
+        <v>1.71138107667851</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1954,34 +1954,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G29" t="n">
-        <v>15.8</v>
+        <v>19.35</v>
       </c>
       <c r="H29" t="n">
-        <v>1.542817329617431</v>
+        <v>1.086738836265223</v>
       </c>
       <c r="I29" t="n">
-        <v>1.84203344898835</v>
+        <v>0.806961722029484</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -1992,11 +1992,11 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2004,37 +2004,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>22.5</v>
+        <v>19.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.560047918538485</v>
+        <v>1.698140741541455</v>
       </c>
       <c r="I30" t="n">
-        <v>1.53</v>
+        <v>2.16766115621638</v>
       </c>
       <c r="J30" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K30" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L30" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M30" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N30" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2045,11 +2045,11 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2057,37 +2057,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>9.859999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G31" t="n">
-        <v>20.85</v>
+        <v>17.91</v>
       </c>
       <c r="H31" t="n">
-        <v>1.703073214823742</v>
+        <v>1.699273096764108</v>
       </c>
       <c r="I31" t="n">
-        <v>1.52091254752852</v>
+        <v>1.05926908510679</v>
       </c>
       <c r="J31" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K31" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L31" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M31" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N31" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2098,49 +2098,49 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>9.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>20.31</v>
+        <v>15.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.560624659028914</v>
+        <v>1.542817329617431</v>
       </c>
       <c r="I32" t="n">
-        <v>1.21254379102751</v>
+        <v>1.84203344898835</v>
       </c>
       <c r="J32" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K32" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L32" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M32" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N32" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2159,41 +2159,41 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>10.03</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>20.01</v>
+        <v>22.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.54444673610395</v>
+        <v>1.560047918538485</v>
       </c>
       <c r="I33" t="n">
-        <v>0.541078316722817</v>
+        <v>1.53</v>
       </c>
       <c r="J33" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K33" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L33" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M33" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N33" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2204,11 +2204,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2216,37 +2216,37 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>9.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>20.96</v>
+        <v>20.85</v>
       </c>
       <c r="H34" t="n">
-        <v>1.604751287768125</v>
+        <v>1.703073214823742</v>
       </c>
       <c r="I34" t="n">
-        <v>0.850441042680259</v>
+        <v>1.52091254752852</v>
       </c>
       <c r="J34" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K34" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L34" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M34" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N34" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2257,11 +2257,11 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2269,37 +2269,37 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>9.85</v>
+        <v>9.99</v>
       </c>
       <c r="G35" t="n">
-        <v>20.73</v>
+        <v>20.31</v>
       </c>
       <c r="H35" t="n">
-        <v>1.589033942558747</v>
+        <v>1.560624659028914</v>
       </c>
       <c r="I35" t="n">
-        <v>2.14788592339205</v>
+        <v>1.21254379102751</v>
       </c>
       <c r="J35" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K35" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L35" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M35" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N35" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2318,41 +2318,41 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F36" t="n">
-        <v>9.94</v>
+        <v>10.03</v>
       </c>
       <c r="G36" t="n">
-        <v>19.92</v>
+        <v>20.01</v>
       </c>
       <c r="H36" t="n">
-        <v>1.482019854132901</v>
+        <v>1.54444673610395</v>
       </c>
       <c r="I36" t="n">
-        <v>0.542826236601442</v>
+        <v>0.541078316722817</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2363,49 +2363,49 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4.3</v>
-      </c>
       <c r="F37" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="G37" t="n">
-        <v>20.75</v>
+        <v>20.96</v>
       </c>
       <c r="H37" t="n">
-        <v>1.473299221677717</v>
+        <v>1.604751287768125</v>
       </c>
       <c r="I37" t="n">
-        <v>0.758892017654233</v>
+        <v>0.850441042680259</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2424,41 +2424,41 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="F38" t="n">
-        <v>9.32</v>
+        <v>9.85</v>
       </c>
       <c r="G38" t="n">
-        <v>22.45</v>
+        <v>20.73</v>
       </c>
       <c r="H38" t="n">
-        <v>1.525052642945845</v>
+        <v>1.589033942558747</v>
       </c>
       <c r="I38" t="n">
-        <v>0.511201323109319</v>
+        <v>2.14788592339205</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2469,49 +2469,49 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="F39" t="n">
-        <v>8.91</v>
+        <v>9.94</v>
       </c>
       <c r="G39" t="n">
-        <v>21.15</v>
+        <v>19.92</v>
       </c>
       <c r="H39" t="n">
-        <v>1.520124887150165</v>
+        <v>1.482019854132901</v>
       </c>
       <c r="I39" t="n">
-        <v>0.601560297020399</v>
+        <v>0.542826236601442</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2522,49 +2522,49 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="F40" t="n">
-        <v>9.68</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>20.15</v>
+        <v>20.75</v>
       </c>
       <c r="H40" t="n">
-        <v>1.510708234496781</v>
+        <v>1.473299221677717</v>
       </c>
       <c r="I40" t="n">
-        <v>0.67004569366047</v>
+        <v>0.758892017654233</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2587,37 +2587,37 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>1.2</v>
       </c>
       <c r="F41" t="n">
-        <v>10.1</v>
+        <v>9.32</v>
       </c>
       <c r="G41" t="n">
-        <v>22.89</v>
+        <v>22.45</v>
       </c>
       <c r="H41" t="n">
-        <v>1.860779140152104</v>
+        <v>1.525052642945845</v>
       </c>
       <c r="I41" t="n">
-        <v>1.84144213994961</v>
+        <v>0.511201323109319</v>
       </c>
       <c r="J41" t="n">
-        <v>0.125</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K41" t="n">
-        <v>0.125</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L41" t="n">
-        <v>0.75</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M41" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N41" t="n">
-        <v>0.625</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2628,11 +2628,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2640,37 +2640,37 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="F42" t="n">
-        <v>10.25</v>
+        <v>9.68</v>
       </c>
       <c r="G42" t="n">
-        <v>20.6</v>
+        <v>20.15</v>
       </c>
       <c r="H42" t="n">
-        <v>1.310133297964056</v>
+        <v>1.510708234496781</v>
       </c>
       <c r="I42" t="n">
-        <v>0.719020334793854</v>
+        <v>0.67004569366047</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2681,49 +2681,49 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="F43" t="n">
-        <v>10.98</v>
+        <v>10.1</v>
       </c>
       <c r="G43" t="n">
-        <v>21.84</v>
+        <v>22.89</v>
       </c>
       <c r="H43" t="n">
-        <v>1.3034886557697</v>
+        <v>1.860779140152104</v>
       </c>
       <c r="I43" t="n">
-        <v>1.07155989004254</v>
+        <v>1.84144213994961</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2742,41 +2742,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="F44" t="n">
-        <v>9.33</v>
+        <v>10.25</v>
       </c>
       <c r="G44" t="n">
-        <v>19.23</v>
+        <v>20.6</v>
       </c>
       <c r="H44" t="n">
-        <v>1.114988392338943</v>
+        <v>1.310133297964056</v>
       </c>
       <c r="I44" t="n">
-        <v>1.16723767030516</v>
+        <v>0.719020334793854</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="N44" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -2787,49 +2787,49 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="F45" t="n">
-        <v>9.77</v>
+        <v>10.98</v>
       </c>
       <c r="G45" t="n">
-        <v>19.85</v>
+        <v>21.84</v>
       </c>
       <c r="H45" t="n">
-        <v>1.603237791932059</v>
+        <v>1.3034886557697</v>
       </c>
       <c r="I45" t="n">
-        <v>1.00433351312142</v>
+        <v>1.07155989004254</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2848,43 +2848,202 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.652212487523566</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.50636152676643</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>S79</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G47" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.114988392338943</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.16723767030516</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G48" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.603237791932059</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.00433351312142</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>S81</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
         <v>1.8</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F49" t="n">
         <v>9.16</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G49" t="n">
         <v>18.84</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H49" t="n">
         <v>-1.079185835773038</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I49" t="n">
         <v>0.942177344013984</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="J49" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>Train</t>
         </is>

--- a/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/site_eval_train.xlsx
@@ -538,19 +538,19 @@
         <v>0.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N2" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -591,19 +591,19 @@
         <v>1.43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N3" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -644,19 +644,19 @@
         <v>1.57</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N4" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         <v>0.87</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1121,19 +1121,19 @@
         <v>7.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N13" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>3.61</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N14" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1227,19 +1227,19 @@
         <v>2.13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N15" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1333,19 +1333,19 @@
         <v>1.12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N17" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>5.486400000000001</v>
@@ -1386,19 +1386,19 @@
         <v>1.53</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1439,19 +1439,19 @@
         <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N19" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1492,19 +1492,19 @@
         <v>2.47</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N20" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>1.8288</v>
@@ -1651,19 +1651,19 @@
         <v>1.55</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1704,19 +1704,19 @@
         <v>1.82</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N24" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1757,19 +1757,19 @@
         <v>0.41342143147169</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N25" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1810,19 +1810,19 @@
         <v>1.08693561108866</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N26" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1863,19 +1863,19 @@
         <v>1.50490599353894</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N27" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1916,19 +1916,19 @@
         <v>1.71138107667851</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N28" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -1969,19 +1969,19 @@
         <v>0.806961722029484</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N29" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         <v>2.16766115621638</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N30" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2075,19 +2075,19 @@
         <v>1.05926908510679</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N31" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2128,19 +2128,19 @@
         <v>1.84203344898835</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N32" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2181,19 +2181,19 @@
         <v>1.53</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N33" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
         <v>1.52091254752852</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N34" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2287,19 +2287,19 @@
         <v>1.21254379102751</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N35" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         <v>0.541078316722817</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K36" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N36" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2393,19 +2393,19 @@
         <v>0.850441042680259</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K37" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N37" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2446,19 +2446,19 @@
         <v>2.14788592339205</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K38" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N38" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2499,19 +2499,19 @@
         <v>0.542826236601442</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N39" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2552,19 +2552,19 @@
         <v>0.758892017654233</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K40" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N40" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2605,19 +2605,19 @@
         <v>0.511201323109319</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K41" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N41" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2658,19 +2658,19 @@
         <v>0.67004569366047</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N42" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2711,19 +2711,19 @@
         <v>1.84144213994961</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N43" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2764,19 +2764,19 @@
         <v>0.719020334793854</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K44" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N44" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -2795,11 +2795,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>3.4</v>
@@ -2817,19 +2817,19 @@
         <v>1.07155989004254</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N45" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2870,19 +2870,19 @@
         <v>1.50636152676643</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K46" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N46" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -2923,19 +2923,19 @@
         <v>1.16723767030516</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K47" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N47" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -2976,19 +2976,19 @@
         <v>1.00433351312142</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N48" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3029,19 +3029,19 @@
         <v>0.942177344013984</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="N49" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
